--- a/daily_matches/job_matches_2026-08-21.xlsx
+++ b/daily_matches/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,55 +473,55 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Devengine</t>
+          <t>Vagaro</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Azure ML, Azure ML Studio, Redshift, BigQuery, Synapse, Kinesis, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Data Lake, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e77377ecd96f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=44fc81c2d0a70c40</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
+          <t>Sr Databricks Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J&amp;T Business Consulting</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.4</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, Azure ML, MLflow, Docker</t>
+          <t>RAG, Kinesis, MLflow, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Kafka, Tableau</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675b9b533569f997</t>
+          <t>https://www.indeed.com/viewjob?jk=37f9cb4e7f9e0916</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer IV, AI &amp; Digital Engineering</t>
+          <t>Senior Backend Software Engineer — IoT Platform</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>X-Energy</t>
+          <t>E-Space</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Saratoga, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.1</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, S3, EC2, Glue, Athena, Data Lake, Kinesis, FastAPI</t>
+          <t>RAG, S3, EC2, FastAPI, CI/CD, Terraform, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3046d8552c476c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d0e8ed3b7baac81e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Databricks Engineer</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, MLflow, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Kafka, Tableau</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e82684b0040295</t>
+          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, BigQuery, Docker, CI/CD, Terraform, Git, Snowflake, BigQuery</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
+          <t>https://www.indeed.com/viewjob?jk=a6e34987b7e0b5fb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - C# and Azure Cloud</t>
+          <t>Automation Developer - Service Enablement</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>AST SpaceMobile</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, SQL, R</t>
+          <t>RAG, Copilot, S3, FastAPI, Jenkins, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
+          <t>https://www.indeed.com/viewjob?jk=50d90ff4d4613640</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Database Architect</t>
+          <t>Automation Developer - Service Enablement</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>AST SpaceMobile</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, CI/CD, Terraform, PostgreSQL, MySQL, MongoDB, Python, SQL</t>
+          <t>RAG, Copilot, S3, FastAPI, Jenkins, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6ab183217fe971</t>
+          <t>https://www.indeed.com/viewjob?jk=2aabaa932870e470</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Software Development Engineer in Test - Datacenter Server OS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Databricks, Kafka, Hadoop, NoSQL, Python, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d39ba4a5a320f</t>
+          <t>https://www.indeed.com/viewjob?jk=fbe6dd3b6aa64aa7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Engineer</t>
+          <t>Senior, Software Engineer, Cryptographic Asset Monitoring</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, PostgreSQL, MongoDB, Cassandra, Python, SQL, R</t>
+          <t>RAG, Copilot, Prompt Engineering, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d14b10e605c9b57</t>
+          <t>https://www.indeed.com/viewjob?jk=cd72638bd627aaf0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, BigQuery, Git, BigQuery, PySpark, Python, SQL</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc515841b0a0665</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GoGuardian</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Data Lake, CI/CD, Terraform, Databricks, PySpark, Python, SQL</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
+          <t>https://www.indeed.com/viewjob?jk=5a76d5a43d9b0fbd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Salesforce Architect / Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, SQL, R</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d30d040cab4dde</t>
+          <t>https://www.indeed.com/viewjob?jk=f511646e76683c01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Nucleus Biologics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, BigQuery, Git, BigQuery, PySpark, Python, SQL</t>
+          <t>S3, EC2, FastAPI, Docker, CI/CD, Terraform, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
+          <t>https://www.indeed.com/viewjob?jk=6733a6ca4e19dc2e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>Red Team - Sr Security Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>WellSky</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Azure ML, Data Lake, Git, PySpark, Power BI, SQL, R</t>
+          <t>RAG, Copilot, Prompt Engineering, Kubernetes, AKS, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=328d91a8632c1090</t>
+          <t>https://www.indeed.com/viewjob?jk=c34e3e61ca8f367f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Java/API Engineering)</t>
+          <t>Data Analyst, Information Technology - KAHE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Southeastern University</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Copilot, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd203382fdc08aa8</t>
+          <t>https://www.indeed.com/viewjob?jk=968d4ad58922e345</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Java/API Engineering)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java, Scala</t>
+          <t>Kubernetes, CI/CD, Jenkins, Terraform, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a797253a3e71756</t>
+          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Java/API Engineering)</t>
+          <t>Assoc Data Scientist, AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Prompt Engineering, Data Lake, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b9bed7af32546c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e6466bc0c9a82bdf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
+          <t>Senior Research Scientist/Software Engineer, LLM/Agent Platform (TikTok-Content Ecology AI Innovation &amp; Platform)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, CI/CD, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R</t>
+          <t>LangChain, RAG, LLaMA, FAISS, TensorFlow, PyTorch, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
+          <t>https://www.indeed.com/viewjob?jk=d05ceed99b18c254</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>Senior Engineer, IAM Platform Engineering</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Azure ML, Data Lake, Git, PySpark, Power BI, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c824b84d56f365</t>
+          <t>https://www.indeed.com/viewjob?jk=8561c51f57e1ceb0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cyber Full Stack Senior Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82d7145d6d7c552d</t>
+          <t>https://www.indeed.com/viewjob?jk=0c266a0adc70f1a2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cyber Full Stack Senior Consultant</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=206c1d648eba9b73</t>
+          <t>https://www.indeed.com/viewjob?jk=01f40b660c79c10d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Salesforce and DevOps Engineer</t>
+          <t>Cyber Full Stack Senior Consultant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecdc1420fc807098</t>
+          <t>https://www.indeed.com/viewjob?jk=102c20ae1138d9fd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Salesforce and DevOps Engineer</t>
+          <t>Cyber Full Stack Senior Consultant</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rancho Belago, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be970bf8d999d1a9</t>
+          <t>https://www.indeed.com/viewjob?jk=a133bb0c750dcd64</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CCB Risk Modeling - AI ML Sr. Associate</t>
+          <t>Cyber Full Stack Senior Consultant</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Git, Hadoop, Python, R, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e45b1cd7a4b8f51</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5557674a34f6ed</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mid-Level Full Stack Engineer</t>
+          <t>Cyber Full Stack Senior Consultant</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ISI Enterprises</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Git, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1046fa9e22fe71</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad6c99951eec476</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer I - Java, Python , GCP , NoSQL - GMNST</t>
+          <t>Cyber Full Stack Senior Consultant</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BigQuery, BigQuery, Kafka, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3ceb359b861a9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=e3473d0aaa2abb34</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II</t>
+          <t>Cyber Full Stack Senior Consultant</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e26ddfd9b828ba4</t>
+          <t>https://www.indeed.com/viewjob?jk=591da3b07088d1b6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Assoc Applications Dev Engineer</t>
+          <t>Cyber Full Stack Senior Consultant</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, Docker, CI/CD, Git, R, Java</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2b19053f73878b</t>
+          <t>https://www.indeed.com/viewjob?jk=2842e9313d735c33</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IT Platform Engineer</t>
+          <t>Cyber Full Stack Senior Consultant</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Loft Orbital Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbdecb2c66b738f2</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ec7dae945266c9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Application Development Senior Advisor- Hybrid</t>
+          <t>Cyber Full Stack Senior Consultant</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bloomfield, CT, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Jenkins, Git, Kafka, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d47b6a52f18e37f</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2031ff61ffa26a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Cyber Full Stack Senior Consultant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MHC Kenworth</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3658d1c1beb1e1</t>
+          <t>https://www.indeed.com/viewjob?jk=2b6e714afe8711cf</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Engineer, FW &amp; Product Test Engineering</t>
+          <t>Cyber Full Stack Senior Consultant</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Git, Python, R, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90c62dab278c84fe</t>
+          <t>https://www.indeed.com/viewjob?jk=ad8f4af96cd8dfba</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Scientist Senior Associate</t>
+          <t>Cyber Full Stack Senior Consultant</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Git, Tableau, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8a8ca87a2541f0</t>
+          <t>https://www.indeed.com/viewjob?jk=ac72ee15051023b8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Technology Development Program – Software Engineer Development Track (2026 Summer Interns Only)</t>
+          <t>Cyber Full Stack Senior Consultant</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ba1e155693d450</t>
+          <t>https://www.indeed.com/viewjob?jk=af69c2c580847682</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Technology Development Program – Software Engineer Development Track (2026 Summer Interns Only)</t>
+          <t>Cyber Full Stack Senior Consultant</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,1337 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52728e5e276fb9ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a3cba95803a2bf93</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac8da07e8ace3092</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7d870e0109955ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=150f6bc080fa727d</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e13b1ecb890a8261</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e84ffd2e54c8a0e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81a1f45b22379680</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a69aabff07b352a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0c6d947ba032350</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c5c3614c86a2fc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0b1067fc76b0b83</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c596c9aff6e12282</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbfb53a419b3cb6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca1d3a393ab8c24e</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d13d39ad7f43c111</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a553e2b890e401dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12a515aa64800086</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=111f2308fbea6650</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1d45d336e2d2efe</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe8e98cf5a174758</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Jericho, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62cf02ee39dcc707</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47f8831c7731ab76</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7dce40f519d05fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=134bed9d4b572ab3</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=074cc2ccf18784f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73339d64999175bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34d7a355ab6e67dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=babc2a64bc215e0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97c23336ccbeb3fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c443e57310d73ecb</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27bf197be7ab7948</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=952aa5b62fe830db</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1769b274b5731e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38d45991dcdec6e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=536a0c139757e256</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Cyber Full Stack Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a734b9795f0b5ea6</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer - Ads Core and Commerce Ads</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>TikTok USDS JV</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Hadoop, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca1d6cdfc3c26a46</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85d2088869dd01ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Data Scientist III, Media &amp; Paid Social Analytics</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Expedia Group</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Tableau, Python, SQL, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=135c1698ee14b8dd</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-21.xlsx
+++ b/daily_matches/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Software Engineer Python - Advanced | Columbus, US | JPMC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, TensorFlow, PyTorch, BigQuery, Data Lake, Git, BigQuery</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, Pinecone, Prompt Engineering, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=618a4e40ef5bde1f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - AI Applications</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, BigQuery, AKS, CI/CD, Terraform, Git, BigQuery, NoSQL, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, TensorFlow, PyTorch, S3, MLflow, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f5a19c2de7ce51c</t>
+          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - AI Applications</t>
+          <t>Full Stack Developer - Advanced | Columbus, US | JPMC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, BigQuery, AKS, CI/CD, Terraform, Git, BigQuery, NoSQL, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, S3, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61a29eb9246b24ea</t>
+          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Engineer; Platform Analytics (Contract)</t>
+          <t>Senior AI Application Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vervint</t>
+          <t>Silgan Containers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Data Lake, Kinesis, Terraform, Kafka, Quicksight, Python</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Copilot, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,102 +601,102 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d72d1f3b94beb684</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Architect</t>
+          <t>Software Engineer iOS/Android – Advanced | Columbus, US</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Data Lake, CI/CD, Git, Snowflake, Databricks, Kafka, SQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc06d4d982f61181</t>
+          <t>https://www.indeed.com/viewjob?jk=c80f07aa82d3c33f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Associate - Cloud Platform Engineer</t>
+          <t>Data Scientist Senior Associate — Business Observability &amp; AI Platform</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python</t>
+          <t>Data Scientist, RAG, BigQuery, AKS, Snowflake, BigQuery, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
+          <t>https://www.indeed.com/viewjob?jk=1d61a48289fe651f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Forward Deployed AI Architect (GenAI, AWS)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, AKS, CI/CD, Terraform, BigQuery, MongoDB, NoSQL, Python, SQL</t>
+          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6693b8193e00cff6</t>
+          <t>https://www.indeed.com/viewjob?jk=b6214d6d05e52a4a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+          <t>Senior Forward Deployed AI Architect (GenAI, AWS)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, MongoDB, NoSQL, SQL, R</t>
+          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=30627f2519238a7d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Forward Deployed AI Architect (GenAI, AWS)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, SQL, R, Java</t>
+          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c46cf07764f26975</t>
+          <t>https://www.indeed.com/viewjob?jk=6b5acd54e336d48b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>Senior Forward Deployed AI Architect (GenAI, AWS)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
+          <t>https://www.indeed.com/viewjob?jk=a53156fdd087b203</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — DevOps &amp; Platform, AI Systems</t>
+          <t>Senior Forward Deployed AI Architect (GenAI, AWS)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Glue, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aca7ea49882dad9</t>
+          <t>https://www.indeed.com/viewjob?jk=7a77018d01dad413</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Senior Forward Deployed AI Architect (GenAI, AWS)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, S3, EC2, Kubernetes, CI/CD, Dask, Python, R</t>
+          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea3bf52be048627</t>
+          <t>https://www.indeed.com/viewjob?jk=7c929e144df1653d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Engineer II - AI Foundations</t>
+          <t>Senior Forward Deployed AI Architect (GenAI, AWS)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Best Buy</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb25ca5c5e2d6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4e1846742306c0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer, Devops Platform Engineering</t>
+          <t>Senior AI/ML Engineer (GenAI, AWS)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>AI Engineer, RAG, S3, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e4f35bce2d70bc</t>
+          <t>https://www.indeed.com/viewjob?jk=1075d7cc0d3e8b57</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI/ML Engineer (GenAI, AWS)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, S3, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,497 +986,112 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb69f45b1c58c41</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Java Python AWS Software Engineer III (ML) - Agentic Treasury</t>
+          <t>Senior Solution Engineer (Guidewire)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, CI/CD, Databricks, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443d36ee3e882eca</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c6535e6b03d8b4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior End-to-End Quality Engineer</t>
+          <t>FDE AI/ Solutions Architect (AI, Python/Data)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, S3, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26112e9d5da37adc</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c055ce9797102c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Associate - AI AppSec Engineer</t>
+          <t>FDE AI/ Solutions Architect (AI, Python/Data)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, CI/CD, Git, Python, R, Scala</t>
+          <t>RAG, S3, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f799f292693d0a5b</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2027 Masters Software Engineer Intern/Co-op</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=341e17f17c298e75</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2027 Masters Software Engineer Intern/Co-op</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ee42344782e7889</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2027 Undergrad Software Engineer Intern/Co-op</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=91aef0c57c0d2292</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2027 Undergrad Software Engineer Intern/Co-op</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=703e6591cf9c4ab2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Software Development Engineering</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Toyota North America</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>CI/CD, Git, Kafka, PostgreSQL, MongoDB, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b334cf16f3f96c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Career Concepts Staffing Services, Inc</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Git, Snowflake, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7022703d9f94abf1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AI Prototyping &amp; Transformation Associate</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1369c7bffe2fa540</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Data Scientist - Conversational AI</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Dearborn, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=626c0af9dfe8658c</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Software Dev Engineer I</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Optimum</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af8b34cea41491bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Software Dev Engineer I</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Optimum</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Bethpage, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d2214b64c665e26</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Database Analyst</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>NYU Langone Health</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4efc4e32f803c73</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ffa2bfcb22c9c8</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-21.xlsx
+++ b/daily_matches/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer Python - Advanced | Columbus, US | JPMC</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, Pinecone, Prompt Engineering, FastAPI, Docker</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, AWS SageMaker, S3, EC2, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618a4e40ef5bde1f</t>
+          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, TensorFlow, PyTorch, S3, MLflow, FastAPI, Docker</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
+          <t>https://www.indeed.com/viewjob?jk=28bd955409ade1d4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Advanced | Columbus, US | JPMC</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, S3, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Terraform, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
+          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Application Developer</t>
+          <t>Software Engineer - AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Silgan Containers</t>
+          <t>NBT Bank</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Norwich, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Copilot, CI/CD, Git, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72d1f3b94beb684</t>
+          <t>https://www.indeed.com/viewjob?jk=5140254e8c3c2f42</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer iOS/Android – Advanced | Columbus, US</t>
+          <t>Software Engineer- React Native</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Solve Education</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, R, Java, Scala</t>
+          <t>TensorFlow, PyTorch, FastAPI, Docker, CI/CD, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80f07aa82d3c33f</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e4d9102ee12369</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist Senior Associate — Business Observability &amp; AI Platform</t>
+          <t>IT Analyst Senior</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Vulcan Materials Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, AKS, Snowflake, BigQuery, Tableau, Python, SQL, R</t>
+          <t>LangChain, CI/CD, Git, Snowflake, PySpark, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d61a48289fe651f</t>
+          <t>https://www.indeed.com/viewjob?jk=ad738591847ea39e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed AI Architect (GenAI, AWS)</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Visto360 AI Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
+          <t>TensorFlow, PyTorch, OpenCV, YOLO, Docker, Kubernetes, Git, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6214d6d05e52a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=c68df308de319668</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed AI Architect (GenAI, AWS)</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>South Coast Terminals</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
+          <t>RAG, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30627f2519238a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=c4cfa0ba5599ea10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed AI Architect (GenAI, AWS)</t>
+          <t>JAVA API with Agentic AI only</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>VaaridaTech</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
+          <t>AI Engineer, CI/CD, Jenkins, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b5acd54e336d48b</t>
+          <t>https://www.indeed.com/viewjob?jk=4cba7dce30a95ba6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed AI Architect (GenAI, AWS)</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>REGARD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53156fdd087b203</t>
+          <t>https://www.indeed.com/viewjob?jk=996708fab93ede84</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed AI Architect (GenAI, AWS)</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>REGARD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a77018d01dad413</t>
+          <t>https://www.indeed.com/viewjob?jk=f5ab1be615875308</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed AI Architect (GenAI, AWS)</t>
+          <t>Senior DevOps Engineer (Data)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>AllStars-IT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,11 +867,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
+          <t>Kubernetes, CI/CD, Git, Hadoop, MongoDB, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,217 +881,42 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c929e144df1653d</t>
+          <t>https://www.indeed.com/viewjob?jk=a01188c31d514d0c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed AI Architect (GenAI, AWS)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>TriNet</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
+          <t>Data Scientist, RAG, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4e1846742306c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior AI/ML Engineer (GenAI, AWS)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Provectus</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>MD, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, S3, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1075d7cc0d3e8b57</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior AI/ML Engineer (GenAI, AWS)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Provectus</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ME, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, S3, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb69f45b1c58c41</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Solution Engineer (Guidewire)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Mercury Insurance Company</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, SQL, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c6535e6b03d8b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>FDE AI/ Solutions Architect (AI, Python/Data)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Provectus</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MD, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, S3, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c055ce9797102c</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>FDE AI/ Solutions Architect (AI, Python/Data)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Provectus</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ME, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, S3, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ffa2bfcb22c9c8</t>
+          <t>https://www.indeed.com/viewjob?jk=6f8317c32538df22</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-21.xlsx
+++ b/daily_matches/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Consultant, Data Engineer | Databricks</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, AWS SageMaker, S3, EC2, Redshift</t>
+          <t>Data Scientist, RAG, S3, EC2, Redshift, Data Lake, CI/CD, Jenkins, Git, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
+          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, FastAPI, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bd955409ade1d4</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>.NET Backend Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Terraform, Databricks, Python, SQL, R</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer - AI</t>
+          <t>Finance Solutions, Google Cloud Platform</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NBT Bank</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norwich, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>CI/CD, GitHub Actions, Git, PySpark, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5140254e8c3c2f42</t>
+          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer- React Native</t>
+          <t>Data Engineer Denodo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Solve Education</t>
+          <t>Flowserve</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, FastAPI, Docker, CI/CD, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Synapse, CI/CD, Git, Snowflake, Databricks, Power BI, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e4d9102ee12369</t>
+          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IT Analyst Senior</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vulcan Materials Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>South Barrington, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, CI/CD, Git, Snowflake, PySpark, Tableau, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad738591847ea39e</t>
+          <t>https://www.indeed.com/viewjob?jk=4aefdd0e82f34e72</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Visto360 AI Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>South Barrington, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, OpenCV, YOLO, Docker, Kubernetes, Git, Python, R</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c68df308de319668</t>
+          <t>https://www.indeed.com/viewjob?jk=a6aaf9d34b158557</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>South Coast Terminals</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>South Barrington, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4cfa0ba5599ea10</t>
+          <t>https://www.indeed.com/viewjob?jk=8ce3c7901c133786</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JAVA API with Agentic AI only</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VaaridaTech</t>
+          <t>Visto360 AI Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, CI/CD, Jenkins, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>TensorFlow, PyTorch, OpenCV, YOLO, Docker, Kubernetes, Git, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cba7dce30a95ba6</t>
+          <t>https://www.indeed.com/viewjob?jk=047db08c8a1f93b9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Senior Network Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>REGARD</t>
+          <t>Blink Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=996708fab93ede84</t>
+          <t>https://www.indeed.com/viewjob?jk=45007f9052dec518</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Senior Network Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>REGARD</t>
+          <t>Blink Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,77 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ab1be615875308</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer (Data)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>AllStars-IT</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Kubernetes, CI/CD, Git, Hadoop, MongoDB, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a01188c31d514d0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>TriNet</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f8317c32538df22</t>
+          <t>https://www.indeed.com/viewjob?jk=ec98f1d39b8867a8</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-21.xlsx
+++ b/daily_matches/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consultant, Data Engineer | Databricks</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Redshift, Data Lake, CI/CD, Jenkins, Git, Databricks</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, S3, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, FastAPI, CI/CD, Terraform, Git, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, S3, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>.NET Backend Developer</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>23.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, S3, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Finance Solutions, Google Cloud Platform</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>23.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CI/CD, GitHub Actions, Git, PySpark, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, S3, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
+          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer Denodo</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Flowserve</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Allentown, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>23.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Synapse, CI/CD, Git, Snowflake, Databricks, Power BI, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, S3, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
+          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Barrington, IL, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>23.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, S3, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aefdd0e82f34e72</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Engineer (Analytics)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Barrington, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>21.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Snowflake, Databricks, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6aaf9d34b158557</t>
+          <t>https://www.indeed.com/viewjob?jk=593e53f5fee30d60</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Engineer- Full Stack USA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>First Solar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Barrington, IL, US USA</t>
+          <t>Perrysburg, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, Matplotlib, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ce3c7901c133786</t>
+          <t>https://www.indeed.com/viewjob?jk=feaf58186fd25df4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Visto360 AI Inc.</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, OpenCV, YOLO, Docker, Kubernetes, Git, Python, R</t>
+          <t>RAG, Copilot, Cortex, CI/CD, GitHub Actions, Git, Snowflake, Databricks, Tableau, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047db08c8a1f93b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8db0ab6465cbf1ff</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Network Engineer II</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Blink Health</t>
+          <t>Accel Entertainment Gaming, LLC.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Burr Ridge, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Hugging Face, TensorFlow, PyTorch, Data Lake, CI/CD, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,42 +811,357 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45007f9052dec518</t>
+          <t>https://www.indeed.com/viewjob?jk=2ba69b40a4faee12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Network Engineer II</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Blink Health</t>
+          <t>Accel Entertainment Gaming, LLC.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Hugging Face, TensorFlow, PyTorch, Data Lake, CI/CD, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=801c5d14516474f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Software Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5841b84dfba34a89</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (AI)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Zuora</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Pinecone, Docker, Kubernetes, Kafka, PostgreSQL, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a02136b2a768b805</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Block Labs</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Malta, MT, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, AKS, Git, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1b041dedd3f712f</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sr Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Health Monitor Network</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Montvale, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Copilot, BigQuery, Git, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09d110ed543c2f75</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Symhas</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Git, PostgreSQL, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc1931bcf1e8f3cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Engineering Architect</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MFS Investment Management</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Snowflake, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd0b3bb72bb11909</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Process Integration Development Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Intel Corporation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Hillsboro, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>10</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec98f1d39b8867a8</t>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, OpenCV, Dataflow, Git, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92d8f3787f613b01</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Digital Twin Platform</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Instacart</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Git, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3eac9c2a2f4c5619</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET), Vault</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Keeper Security, Inc.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1fb1abe7846a5125</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-21.xlsx
+++ b/daily_matches/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, S3, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Data Lake, FastAPI, Kubernetes, AKS, CI/CD, Terraform, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e7b1c586e6a4d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Data Scientist, P&amp;C Insurance - Remote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Upland Capital Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.3</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, S3, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Azure ML, MLflow, Docker, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e343468716abb0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, S3, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, Machine Learning Engineer, XGBoost, Kubernetes, AKS, CI/CD, Git, Databricks, PySpark, Tableau</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef1c00bbfcfa5af</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>23.3</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, S3, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, BigQuery, CI/CD, Snowflake, Databricks, BigQuery, Hadoop, NoSQL, Power BI, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Allentown, PA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>23.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, S3, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Synapse, Docker, AKS, Git, Databricks, PySpark, PostgreSQL, Power BI, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>23.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, S3, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Synapse, Docker, AKS, Git, Databricks, PySpark, PostgreSQL, Power BI, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Analytics)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21.1</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Snowflake, Databricks, PySpark, Kafka</t>
+          <t>RAG, Synapse, Docker, AKS, Git, Databricks, PySpark, PostgreSQL, Power BI, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=593e53f5fee30d60</t>
+          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engineer- Full Stack USA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>First Solar</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Perrysburg, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, Matplotlib, Python</t>
+          <t>RAG, Synapse, Docker, AKS, Git, Databricks, PySpark, PostgreSQL, Power BI, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaf58186fd25df4</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
         </is>
       </c>
     </row>
@@ -753,12 +753,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Cortex, CI/CD, GitHub Actions, Git, Snowflake, Databricks, Tableau, Python</t>
+          <t>RAG, Synapse, Docker, AKS, Git, Databricks, PySpark, PostgreSQL, Power BI, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db0ab6465cbf1ff</t>
+          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Machine Learning Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Accel Entertainment Gaming, LLC.</t>
+          <t>XPO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Burr Ridge, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Hugging Face, TensorFlow, PyTorch, Data Lake, CI/CD, Databricks, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, BigQuery, Docker, Kubernetes, CI/CD, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ba69b40a4faee12</t>
+          <t>https://www.indeed.com/viewjob?jk=2fd483c881d64939</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Machine Learning Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Accel Entertainment Gaming, LLC.</t>
+          <t>XPO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Hugging Face, TensorFlow, PyTorch, Data Lake, CI/CD, Databricks, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, BigQuery, Docker, Kubernetes, CI/CD, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=801c5d14516474f9</t>
+          <t>https://www.indeed.com/viewjob?jk=184659d765737611</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI/ML Software Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Mossville, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Docker, Git, Snowflake, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5841b84dfba34a89</t>
+          <t>https://www.indeed.com/viewjob?jk=ab38c6d425e57a4d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI)</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Zuora</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Pinecone, Docker, Kubernetes, Kafka, PostgreSQL, MySQL, SQL, R</t>
+          <t>Data Scientist, RAG, Redshift, Synapse, Snowflake, Redshift, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02136b2a768b805</t>
+          <t>https://www.indeed.com/viewjob?jk=00eec4e6432a7078</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>AI Engineer/DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Block Labs</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malta, MT, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, AKS, Git, Kafka, Python, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, Kubernetes, AKS, CI/CD, Git, Databricks, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b041dedd3f712f</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Power BI Developer</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Health Monitor Network</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Copilot, BigQuery, Git, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09d110ed543c2f75</t>
+          <t>https://www.indeed.com/viewjob?jk=35d8b1b2a9a4c35b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Business Analytics Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Creve Coeur, MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, PostgreSQL, NoSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Gemini, Copilot, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1931bcf1e8f3cf</t>
+          <t>https://www.indeed.com/viewjob?jk=f23e9d83a038ee73</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineering Architect</t>
+          <t>Senior AI Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MFS Investment Management</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Snowflake, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Data Lake, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0b3bb72bb11909</t>
+          <t>https://www.indeed.com/viewjob?jk=aa69cba61b045c24</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Process Integration Development Engineer</t>
+          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Slavic401K</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, OpenCV, Dataflow, Git, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Copilot, Synapse, Data Lake, Databricks, Power BI, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92d8f3787f613b01</t>
+          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Digital Twin Platform</t>
+          <t>Technical Systems Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Git, Kafka, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Git, Snowflake, MongoDB, Cassandra, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,42 +1126,462 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eac9c2a2f4c5619</t>
+          <t>https://www.indeed.com/viewjob?jk=d47f9514089ab269</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET), Vault</t>
+          <t>Technology Risk Specialist | Technology Risk Management</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7cabbb42d775b97c</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BrainWaves Digital, LLC</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, CI/CD, Git, MongoDB, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=902a93907ef06495</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Engineer II, Software Assurance, Product Security (Remote)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, S3, AKS, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0db0c748ed4ed25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Engineer - Vehicle Configuration Optimization</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, Data Lake, Snowflake, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cec6118fc276a50a</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Everforth ECS</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Data Lake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AI Engineer/DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>10</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, MySQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb1abe7846a5125</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78f03c78f0e5bc9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Founding Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>David Joseph &amp; Company</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, FastAPI, CI/CD, BigQuery, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58354af44a5218a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Altamira Technologies Corp.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Fairborn, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Keras, Docker, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bcf4ab84cceca3b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Quality Assurance Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Telligen</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>West Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3c25db7973d970d</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CoStar Group</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52e5ac29045dcc12</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Systems Engineer II (Remote)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d0d482969ae5966</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sunbelt Rentals</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Fort Mill, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, MLflow, Databricks, Python, SQL, R, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a50bbdfd4f2f1874</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AI Research Scientist II (Full Time)- United States ENG/CPO/AISWP ETR</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, Docker, Kubernetes, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aabcb53dbc386fd9</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-21.xlsx
+++ b/daily_matches/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Platform System Administrator III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Boston Scientific</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Arden Hills, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Data Lake, FastAPI, Kubernetes, AKS, CI/CD, Terraform, Databricks</t>
+          <t>Generative AI, RAG, Cortex, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e7b1c586e6a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=62388f603bbe60a4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist, P&amp;C Insurance - Remote</t>
+          <t>Senior Data Science Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Upland Capital Group</t>
+          <t>LegitScript</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Azure ML, MLflow, Docker, CI/CD, Git, Snowflake</t>
+          <t>Generative AI, RAG, Prompt Engineering, MLflow, Docker, Apache Airflow, CI/CD, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e343468716abb0</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>AI Security &amp; Process Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>TikTok USDS JV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, XGBoost, Kubernetes, AKS, CI/CD, Git, Databricks, PySpark, Tableau</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef1c00bbfcfa5af</t>
+          <t>https://www.indeed.com/viewjob?jk=9b53c9f448f04e1b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
+          <t>Data Engineer Microsoft Fabric</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bilzin Sumberg Baena Price &amp; Axelrod LLP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Snowflake, Databricks, BigQuery, Hadoop, NoSQL, Power BI, Python</t>
+          <t>S3, Synapse, Dataflow, Apache Airflow, CI/CD, Git, Snowflake, Databricks, PySpark, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
+          <t>https://www.indeed.com/viewjob?jk=371409082795e582</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Docker, AKS, Git, Databricks, PySpark, PostgreSQL, Power BI, Python</t>
+          <t>RAG, BigQuery, Dataflow, AKS, CI/CD, BigQuery, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
+          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>ＡＮＧＥＬ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Docker, AKS, Git, Databricks, PySpark, PostgreSQL, Power BI, Python</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8857b0d796476441</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II, Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Credit Acceptance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Docker, AKS, Git, Databricks, PySpark, PostgreSQL, Power BI, Python</t>
+          <t>RAG, S3, Glue, CI/CD, Databricks, PySpark, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
+          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist/Sr Data Scientist, IT Operations Research and Advanced Analytics</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Docker, AKS, Git, Databricks, PySpark, PostgreSQL, Power BI, Python</t>
+          <t>Data Scientist, Azure ML, Databricks, Tableau, Power BI, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
+          <t>https://www.indeed.com/viewjob?jk=e38862b3ec9da4c3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Tech Desires Global LLP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Docker, AKS, Git, Databricks, PySpark, PostgreSQL, Power BI, Python</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=e48d3d108018da35</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Hybrid</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XPO</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, BigQuery, Docker, Kubernetes, CI/CD, BigQuery, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, BigQuery, CI/CD, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fd483c881d64939</t>
+          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Hybrid</t>
+          <t>Sr Backend &amp; Data Engineer (Ad Factory)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>XPO</t>
+          <t>ＡＮＧＥＬ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, BigQuery, Docker, Kubernetes, CI/CD, BigQuery, Python, SQL</t>
+          <t>RAG, S3, Kubernetes, Terraform, Snowflake, PostgreSQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=184659d765737611</t>
+          <t>https://www.indeed.com/viewjob?jk=33fb7411a69b4809</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Elsevier</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mossville, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Docker, Git, Snowflake, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, Gemini, TensorFlow, PyTorch, Matplotlib, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab38c6d425e57a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=00c5df11ebd456f3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, Synapse, Snowflake, Redshift, Tableau, Power BI, Python, SQL</t>
+          <t>RAG, FastAPI, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00eec4e6432a7078</t>
+          <t>https://www.indeed.com/viewjob?jk=8844c85dab974129</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Engineer/DevOps Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Zillow</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Kubernetes, AKS, CI/CD, Git, Databricks, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Databricks, Tableau, Python, SQL, R, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
+          <t>https://www.indeed.com/viewjob?jk=66233eec66c37da7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Associate, Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, Snowflake, Databricks, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d8b1b2a9a4c35b</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Business Analytics Engineer</t>
+          <t>Senior Detection Engineer (AI-ML Focus)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Creve Coeur, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Data Lake, Kubernetes, CI/CD, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,567 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f23e9d83a038ee73</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior AI Developer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Data Lake, Hadoop, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa69cba61b045c24</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Slavic401K</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Boca Raton, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Synapse, Data Lake, Databricks, Power BI, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Technical Systems Engineer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Research Triangle Park, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Git, Snowflake, MongoDB, Cassandra, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d47f9514089ab269</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Technology Risk Specialist | Technology Risk Management</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7cabbb42d775b97c</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Forward Deployed Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>BrainWaves Digital, LLC</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Docker, CI/CD, Git, MongoDB, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=902a93907ef06495</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Engineer II, Software Assurance, Product Security (Remote)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, S3, AKS, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0db0c748ed4ed25</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Data Engineer - Vehicle Configuration Optimization</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Auburn Hills, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Data Scientist, Data Lake, Snowflake, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cec6118fc276a50a</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Everforth ECS</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Data Lake, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AI Engineer/DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=78f03c78f0e5bc9b</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Founding Forward Deployed Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>David Joseph &amp; Company</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, FastAPI, CI/CD, BigQuery, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58354af44a5218a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Altamira Technologies Corp.</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Fairborn, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Keras, Docker, CI/CD, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf4ab84cceca3b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Quality Assurance Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Telligen</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>West Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3c25db7973d970d</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>CoStar Group</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52e5ac29045dcc12</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Systems Engineer II (Remote)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0d482969ae5966</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Sr. Data Scientist</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Sunbelt Rentals</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Fort Mill, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, MLflow, Databricks, Python, SQL, R, Optimization, Bayesian</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a50bbdfd4f2f1874</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>AI Research Scientist II (Full Time)- United States ENG/CPO/AISWP ETR</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, PyTorch, Docker, Kubernetes, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aabcb53dbc386fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=033253dbbdb44ad3</t>
         </is>
       </c>
     </row>
